--- a/output/graficos_dimensiones/comunal_d_depmen_a_2021_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmen_a_2021_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:04</t>
+    <t xml:space="preserve">2026-09-10 01:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmen_a_2021_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmen_a_2021_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:16</t>
+    <t xml:space="preserve">2026-09-12 22:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmen_a_2021_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmen_a_2021_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:28</t>
+    <t xml:space="preserve">2026-09-23 23:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
